--- a/data/trans_orig/Q23-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q23-Edad-trans_orig.xlsx
@@ -677,22 +677,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,36; 15,93</t>
+          <t>15,39; 15,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,43; 15,94</t>
+          <t>15,43; 15,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,37; 16,08</t>
+          <t>15,36; 16,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,56; 16,11</t>
+          <t>15,51; 16,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -702,22 +702,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,9; 15,63</t>
+          <t>14,92; 15,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,54; 15,93</t>
+          <t>15,54; 15,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,27; 15,68</t>
+          <t>15,27; 15,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,26; 15,78</t>
+          <t>15,24; 15,77</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,26; 16,65</t>
+          <t>16,27; 16,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -797,37 +797,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,32; 16,89</t>
+          <t>16,29; 16,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,54; 17,13</t>
+          <t>16,52; 17,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,65; 17,32</t>
+          <t>16,64; 17,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,45; 17,15</t>
+          <t>16,47; 17,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,43; 16,77</t>
+          <t>16,42; 16,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,58; 16,99</t>
+          <t>16,59; 16,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,45; 16,94</t>
+          <t>16,45; 16,92</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,38; 17,13</t>
+          <t>16,38; 17,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,47; 17,1</t>
+          <t>16,47; 17,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,55; 17,41</t>
+          <t>16,56; 17,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,84; 17,66</t>
+          <t>16,8; 17,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,89; 17,61</t>
+          <t>16,88; 17,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,73; 17,41</t>
+          <t>16,77; 17,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,67; 17,23</t>
+          <t>16,66; 17,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,73; 17,2</t>
+          <t>16,73; 17,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,74; 17,3</t>
+          <t>16,73; 17,29</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,99; 16,57</t>
+          <t>15,95; 16,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,1; 16,72</t>
+          <t>16,07; 16,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,08; 16,8</t>
+          <t>16,11; 16,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,59; 18,71</t>
+          <t>17,57; 18,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,39; 18,47</t>
+          <t>17,41; 18,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,28; 18,05</t>
+          <t>17,28; 18,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,65; 17,21</t>
+          <t>16,66; 17,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,71; 17,34</t>
+          <t>16,73; 17,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,75; 17,27</t>
+          <t>16,72; 17,26</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,85; 16,73</t>
+          <t>15,89; 16,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,16; 17,17</t>
+          <t>16,18; 17,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,93; 16,88</t>
+          <t>15,91; 16,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20,16; 23,97</t>
+          <t>20,15; 23,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,03; 21,4</t>
+          <t>18,91; 21,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,73; 21,01</t>
+          <t>18,69; 20,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,89; 18,08</t>
+          <t>16,92; 18,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,11; 18,15</t>
+          <t>17,09; 18,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,14; 18,28</t>
+          <t>17,17; 18,2</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,01; 17,66</t>
+          <t>16,03; 17,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,85; 16,9</t>
+          <t>15,81; 16,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,96; 17,23</t>
+          <t>15,95; 17,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,16; 30,58</t>
+          <t>21,26; 30,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23,66; 34,91</t>
+          <t>23,94; 34,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,0; 25,56</t>
+          <t>20,95; 25,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,81; 18,68</t>
+          <t>16,78; 18,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,89; 18,92</t>
+          <t>16,94; 18,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,27; 18,86</t>
+          <t>17,31; 18,98</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,19; 16,8</t>
+          <t>15,19; 16,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,71; 16,97</t>
+          <t>15,67; 17,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,53; 17,73</t>
+          <t>15,56; 17,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,89; 36,42</t>
+          <t>15,78; 35,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,75; 36,5</t>
+          <t>22,16; 36,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,81; 23,06</t>
+          <t>18,82; 23,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,51; 17,93</t>
+          <t>15,53; 18,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,29; 18,17</t>
+          <t>16,26; 18,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,93; 17,97</t>
+          <t>15,85; 17,85</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,19; 16,51</t>
+          <t>16,19; 16,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,32; 16,6</t>
+          <t>16,31; 16,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,31; 16,67</t>
+          <t>16,3; 16,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,21; 17,74</t>
+          <t>17,2; 17,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,41; 17,97</t>
+          <t>17,38; 17,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,39; 17,92</t>
+          <t>17,41; 17,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,64; 16,91</t>
+          <t>16,62; 16,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,77; 17,07</t>
+          <t>16,79; 17,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,83; 17,12</t>
+          <t>16,81; 17,13</t>
         </is>
       </c>
     </row>
